--- a/Result/checksun_type/手工具機.xlsx
+++ b/Result/checksun_type/手工具機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>77.02000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>90.29</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>25541632.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>18478448.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>18478448.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>22340328.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>35628392.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>35628392.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1689715.322497111</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>25541632</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>25541632.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>76.44000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>82.46</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>90.77</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>90.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>11993989.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>18530460.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>18530460.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>21012225.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>36928818.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>36928818.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-2447746.38427645</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>11993989</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>11993989.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>76.28</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>83.21</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>91.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>83.20999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>12838922.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>22521596.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>22521596.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>22945115.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>38908292.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>38908292.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1991695.208808493</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>12838922</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>12838922.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>76.82000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>83.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>92.05</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>92.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>17519372.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>23921080.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>23921080</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24389345.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>43309022.62</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>43309022.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1359590.093539681</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>17519372</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>17519372.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>77.75999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>84.76</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>92.65</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>92.65000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>24498327.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>24703031.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>24703031.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>24565406.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>44269123.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>44269123.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-909502.7826721072</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>24498327</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>24498327.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>78.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>85.44</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>93.16</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>93.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>25801691.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>26202208.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>26202208.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>23518410.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>44891065.02</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>44891065.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-981783.8463372774</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>25801691</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>25801691.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>80.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>86.25</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>93.7</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>93.7</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>31949669.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>23493990.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>23493990.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>23233683.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>46183811.22</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>46183811.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1189624.942775473</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>31949669</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>31949669.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>81.76</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>86.96</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>94.29</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>94.29000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>19836341.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>23368634.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>23368634.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>23837111.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>47827868.46</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>47827868.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2102766.118302345</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>19836341</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>19836341.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>82.88</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>87.49</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>94.84</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>94.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>21429129.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>24857611.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>24857611.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>23731992.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>49953212.14</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>49953212.14</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2034298.150544219</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>21429129</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>21429129.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>83.82000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>88.1</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>95.44</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>95.44</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>31994214.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>24427782.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>24427782.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>23576187.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>52965825.02</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>52965825.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2034489.119798888</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>31994214</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>31994214.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>84.86</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>88.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>96.09</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>96.09</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>12260600.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>20834612.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>20834612.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>23290139.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>56233928.78</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>56233928.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-3094075.000169881</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>12260600</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>12260600.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>14.28</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>14.88</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>16.09</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2109.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1826.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1826.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>3087.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>3994.46</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>3994.46</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-416.1291410816912</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2109</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2109.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>14.17</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>16.15</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16.15</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1442.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1958.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1958.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3242.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>4217.06</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>4217.06</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-427.5095529198452</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1442</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1442.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>14.19</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>16.23</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1550.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2490.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2490.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>3518.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>4258.64</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>4258.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-357.034800084356</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1550</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1550.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>14.32</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>16.31</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>16.31</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2432.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3483.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3483.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3662.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>4294.64</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>4294.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-255.1767674592165</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2432</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2432.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>14.51</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>15.18</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16.39</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1600.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3719.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3719.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3898.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>4371.26</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>4371.26</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-195.0518362997591</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1600</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>14.65</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>16.47</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16.47</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2768.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>4349.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>4349.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>4053.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>4446.48</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>4446.48</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-13.05008334697095</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2768</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2768.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>16.55</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>4102.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>4526.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>4526.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>4166.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>4488.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>4488.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>122.2756381336894</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>4102</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>4102.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>15.47</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>16.63</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>16.63</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>6515.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>4546.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>4546.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>4170.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>4500.94</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>4500.94</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>168.302538887001</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>6515</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>6515.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>16.71</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>16.71</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>3612.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3841.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3841.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3829.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>4467.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>4467.94</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-30.49126499708973</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>3612</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>3612.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>16.78</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16.78</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>4749.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>4077.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>4077.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3684.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>4569.74</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>4569.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-2.357725367323383</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>4749</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>4749.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>16.86</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3655.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3758.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3758</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3694.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4706.84</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4706.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-83.90417856168142</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3655</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3655.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>61.3</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>63.08</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>67.54</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>67.54000000000001</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>7445486.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7769741.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7769741.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>8691423.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>15009892.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>15009892.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1347155.98855566</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>7445486</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>7445486.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>60.73999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>67.73</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>67.73</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>5001022.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>7111890.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>7111890</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>9146760.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>16055907.42</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>16055907.42</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1452250.377329927</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>5001022</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>5001022.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>60.32000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>63.81</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>67.99</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>67.98999999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3674469.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>8389859.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>8389859.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>10011946.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>16597288.9</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>16597288.9</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1288612.276388524</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3674469</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3674469.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>60.35999999999999</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>64.32</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>68.26</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>68.26000000000001</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>13333730.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>8908116.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>8908116.800000001</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>11221822.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>17511323.92</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>17511323.92</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-866691.0151726454</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>13333730</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>13333730.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>60.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>64.84</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>68.55</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>68.55</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>9393999.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>8866237.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>8866237.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11340663.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>18560543.74</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>18560543.74</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1267913.92717951</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>9393999</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>9393999.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>60.71999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>65.31</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>68.83</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>68.83</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>4156230.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>9613106.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>9613106.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11087909.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>19229318.18</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>19229318.18</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1373692.839790048</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>4156230</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>4156230.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>61.23999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>65.81</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>69.14</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>69.14</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>11390870.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>11181631.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>11181631.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>11977661.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>21222518.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>21222518.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-914555.5778125972</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>11390870</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>11390870.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>61.8</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>66.26</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>69.53</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>69.53</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>6265755.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>11634033.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>11634033.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>13607288.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>23299683.06</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>23299683.06</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1001122.504351506</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>6265755</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>6265755.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>62.16</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>66.68</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>69.94</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>69.94</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>13124334.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>13535527.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>13535527.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>14131075.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>29247760.02</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>29247760.02</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-539915.7028231081</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>13124334</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>13124334.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>62.76000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>70.33</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>70.33</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>13128344.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>13815089.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>13815089</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>14150651.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>32105840.16</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>32105840.16</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-596613.8898245711</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>13128344</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>13128344.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>63.34</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>67.44</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>70.66</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>70.66</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>11998855.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>12562712.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>12562712.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>13871902.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>34024095.08</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>34024095.08</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-656733.3037614953</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>11998855</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>11998855.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>27.2</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>30.33</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>30.33</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>90130496.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>102891471.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>102891471.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>139976545.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>162929477.08</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>162929477.08</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-8302235.025979221</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>90130496</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>90130496.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>26.99</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>30.41</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>116543934.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>110660624.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>110660624.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>154792338.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>167930362.34</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>167930362.34</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-6234570.233193085</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>116543934</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>116543934.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>26.85</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>30.48</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>30.48</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>105477076.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>123333532.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>123333532.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>155136214.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>169872793.4</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>169872793.4</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-5888111.378027424</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>105477076</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>105477076.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>29.58</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>30.55</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>30.55</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>106737599.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>132241859.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>132241859.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>153400791.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>175800706.34</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>175800706.34</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-3997145.678575486</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>106737599</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>106737599.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>27.16</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>30.65</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>95568253.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>148004191.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>148004191.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>154119988.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>183315477.76</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>183315477.76</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1288066.94083789</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>95568253</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>95568253.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>27.35</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>30.76</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>128976262.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>177061620.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>177061620.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>155197777.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>212132753.64</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>212132753.64</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>3824763.575245768</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>128976262</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>128976262.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>27.75</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>30.85</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>179908472.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>198924052.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>198924052.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>151303002.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>221958679.64</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>221958679.64</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>7412778.934820741</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>179908472</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>179908472.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>28.34</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>30.51</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>30.94</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>150018713.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>186938896.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>186938896.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>144140116.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>249744552.38</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>249744552.38</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>6816750.557969987</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>150018713</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>150018713.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>28.82</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>30.68</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>31.06</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>31.06</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>185549258.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>174559723.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>174559723.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>137660190.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>308682445.76</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>308682445.76</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>8924300.249684244</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>185549258</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>185549258.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>31.11</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>31.11</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>240855396.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>160235785.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>160235785.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>132464211.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>323808057.5</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>323808057.5</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>7809516.407501608</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>240855396</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>240855396.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>31.1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>238288422.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>133333934.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>133333934.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>124708175.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>321307698.24</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>321307698.24</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>12399.11840137839</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>238288422</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>238288422.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>29.63</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>30.54</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>30.27</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>30.27</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3654.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>3085.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>3085.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>11875.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-3114.910783354439</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3654</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3654.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>29.59</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>30.14</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>30.14</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>3244.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>3235.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>3235.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>12041.9</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-3137.113031350655</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3244</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3244.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>29.41</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>30.84</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>30</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>3695.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>8867.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>8867.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>12166.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>0</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-3012.862205939868</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>3695</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>3695.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>31.04</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>29.86</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>29.86</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1700.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>13823.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>13823</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>12153.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>0</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-2776.08023371232</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1700</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>30.63</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>29.73</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>29.73</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>3136.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>20554.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>20554.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>12595.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>0</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-2124.924550754669</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>3136</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>3136.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>30.77</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>29.6</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>4401.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>20666.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>20666</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>12858.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>0</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-1272.669126859644</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>4401</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>4401.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>30.89</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>31.52</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>29.45</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>31406.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>20848.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>20848.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>12796.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>0</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-145.2446239074743</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>31406</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>31406.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>31.05</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>31.67</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>29.29</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>28472.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>15465.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>15465</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>10816.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>0</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-1422.843740264823</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>28472</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>28472.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>30.56</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>31.63</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>29.07</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>35359.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>10483.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>10483.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>11079.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>0</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-2882.812344337293</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>35359</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>35359.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>30.23</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>28.86</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>3692.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>4635.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>4635.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>8206.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-5603.417052143064</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>3692</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>3692.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>30.29</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>31.71</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>28.69</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>5314.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>5051.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>5051.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>9542.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>0</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-5896.980311431909</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>5314</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>5314.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>98.11999999999999</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>95.74</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>92.75</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>92.75</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>17465827.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>9367492.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>9367492</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>12240908.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>9547426.36</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>9547426.359999999</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-326158.3432660736</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>17465827</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>17465827.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>95.32</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>92.63</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>95.31999999999999</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>92.63</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>4767854.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>6396828.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>6396828.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>13157633.9</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>9422199.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>9422199.199999999</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1040222.663576726</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>4767854</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>4767854.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>94.96</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>92.58</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>92.58</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>4911165.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>10719716.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>10719716</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>13958338.6</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>9431646.58</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>9431646.58</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-662666.6331784893</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>4911165</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>4911165.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>97.62</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>94.65</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>92.52</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>92.52</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>3178824.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>10818731.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>10818731.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>15737578.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>9398530.84</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>9398530.84</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-114988.9599960633</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>3178824</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>3178824.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>94.35</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>92.46</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>92.45999999999999</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>16513790.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>15976158.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>15976158.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>17604730.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>9405507.58</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>9405507.58</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>857122.4288358316</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>16513790</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>16513790.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>97.28</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>93.94</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>92.38</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>92.38</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2612508.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>15114325.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>15114325.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>16508494.6</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>9131262.26</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>9131262.26</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>786495.1118515488</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2612508</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2612508.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>97.56</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>93.62</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>92.32</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>92.31999999999999</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>26382293.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>19918439.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>19918439.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>16478862.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>9118251.56</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>9118251.560000001</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>2146932.905022157</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>26382293</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>26382293.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>97.36</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>93.34</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>92.26</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>92.26000000000001</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>5406241.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>17196961.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>17196961.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>14023526.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>8669218.56</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>8669218.560000001</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>1466976.612943662</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>5406241</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>5406241.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>97.26</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>92.2</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>28965961.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>20656425.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>20656425</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>13799206.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>8799268.96</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>8799268.960000001</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>2690652.602369256</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>28965961</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>28965961.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>96.53999999999999</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>92.76</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>92.15</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>92.15000000000001</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>12204623.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>19233301.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>19233301.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>12350224.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>8337280.94</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>8337280.94</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>1818410.708606917</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>12204623</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>12204623.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>95.7</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>92.41</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>92.14</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>92.14</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>26633080.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>17902664.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>17902664</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>11808340.8</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>8219127.92</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>8219127.92</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>2303265.263639044</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>26633080</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>26633080.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>23.47</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>24.94</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>24.94</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>240823.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>412205.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>412205.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>693193.9</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>997514.84</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>997514.84</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-319095.1893884297</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>240823</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>240823.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>23.42000000000001</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>24.97</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>24.97</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>153457.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>607422.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>607422.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>730890.9</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1002374.8</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1002374.8</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-304315.0915177257</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>153457</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>153457.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>23.52</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>25.01</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>720646.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>730919.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>730919.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>866247.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1013514.24</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1013514.24</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-262971.6270053727</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>720646</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>720646.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>23.73</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>25.06</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>753131.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>783462.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>783462</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1030108.1</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1003474.7</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1003474.7</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-255287.9410232478</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>753131</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>753131.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>23.99</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>24.58</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>25.11</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>192971.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>790804.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>790804</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1954651.5</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1011006.92</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1011006.92</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-238674.3560122389</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>192971</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>192971.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>24.21</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>24.66</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>25.14</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>25.14</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1216908.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>974182.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>974182.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3458856.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1032384.6</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1032384.6</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-146399.4361389321</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1216908</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1216908.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>24.47000000000001</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>770942.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>854359.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>854359.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>3386415.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1072448.5</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1072448.5</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-119057.1064578181</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>770942</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>770942.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>24.61</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>24.77</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>25.18</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>983358.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>1001575.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>1001575</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3370830.4</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1067290.02</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1067290.02</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-27962.52453987557</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>983358</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>983358.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>24.67</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>24.79</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>789841.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1276754.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1276754.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3289899.3</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>1072378.26</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>1072378.26</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>80412.39693360915</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>789841</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>789841.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>24.71</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>1109862.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>3118499.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>3118499</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3225697.6</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1075061.96</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1075061.96</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>253095.8062909581</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>1109862</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>1109862.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>25.18</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>617793.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>5943530.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>5943530.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>3168018.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1068686.12</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1068686.12</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>456459.2908624946</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>617793</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>617793.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>16.89</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>17.41</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>17.41</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>2590748.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1833531.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1833531.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1462935.3</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1274081.66</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1274081.66</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>126614.9941695766</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>2590748</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>2590748.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>16.79</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>17.41</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>17.41</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>505678.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1513096.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1513096.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1346153.5</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1318151.52</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1318151.52</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>34261.03528551315</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>505678</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>505678.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>16.76</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>17.42</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>316330.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1612284.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1612284</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1416020.7</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1339651.68</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1339651.68</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>124503.5570480824</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>316330</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>316330.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>16.77</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>17.44</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>4401705.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1872712.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1872712.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1498839.7</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1344730.82</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1344730.82</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>269262.1753857499</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>4401705</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>4401705.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>16.85</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>17.46</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>17.46</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1353195.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1167180.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1167180</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1138976.2</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1289754.96</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1289754.96</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>28724.94531864114</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1353195</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1353195.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>16.93</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>17.48</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>988573.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1092339.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1092339.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1060935.0</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1289112.44</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1289112.44</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>10700.51146139158</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>988573</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>988573.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>16.99</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>17.21</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>17.51</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>1001617.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1179210.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1179210.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1023155.3</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1306574.12</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1306574.12</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>23635.80197027093</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1001617</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1001617.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>17.05</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>17.26</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>17.53</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>17.53</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1618474.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1219757.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1219757.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1071371.1</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1310167.08</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1310167.08</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>39873.08119830303</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1618474</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1618474.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>17.55</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>874041.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1124966.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1124966.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>983576.3</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>1305581.38</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>1305581.38</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-4446.665661590407</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>874041</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>874041.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>17.09</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>17.33</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>17.56</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>978992.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1110772.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1110772.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1053702.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>1326261.96</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>1326261.96</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>12158.89831219031</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>978992</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>978992.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>17.1</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>17.58</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>1422930.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1029530.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1029530.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1108537.3</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>1346243.66</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>1346243.66</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>24202.136192156</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1422930</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1422930.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>24.44</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>25.91</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>25.91</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>539777.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>264273.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>264273</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>0</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>44881.51406765514</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>539777</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>539777.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>24.64</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>506472.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>0</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>0</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>22415.69480793941</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>506472</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>506472.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>24.92</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>26.02</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>26.02</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>118514.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>0</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>0</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-6910.500377652337</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>118514</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>118514.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>25.24</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>26.07</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>24600.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>0</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>0</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-6991.332772152935</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>24600</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>24600.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>25.56</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>25.74</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>26.11</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>26.11</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>132002.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>0</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>0</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>3205.097120423074</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>132002</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>132002.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>25.61</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>26.14</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>26.14</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>0</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>0</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>7191.902127247391</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>0</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>25.68</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>25.8</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>26.16</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>28555.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>195176.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>195176</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>184695.0</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>0</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>7191.902127247391</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>28555</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>28555.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>25.74</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>26.2</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>239420.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>194500.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>194500.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>182076.2</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>0</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>22566.6290206922</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>239420</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>239420.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>25.74</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>26.22</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>26.22</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>367406.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>192291.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>192291.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>170174.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>0</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>21131.89497487433</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>367406</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>367406.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>25.64</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>25.83</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>26.23</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>26.23</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>12180.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>182809.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>182809.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>142589.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>0</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>4614.778660317592</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>12180</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>12180.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>26.26</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>26.26</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>328319.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>181039.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>181039</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>149562.6</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>0</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>18914.01325879659</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>328319</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>328319.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>31.49</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>32.14</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>3040182.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>2456523.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>2456523</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>3732357.5</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>7654335.3</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>7654335.3</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-2510959.699003746</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>3040182</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>3040182.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>32.57</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>32.17</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>2456462.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>2783562.0</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>2783562</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>3920197.9</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>7978127.08</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>7978127.08</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-2647451.513904463</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>2456462</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>2456462.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>31.35</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>32.22</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>32.22</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>2462064.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>2895590.6</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>2895590.6</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>4503246.3</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>8193565.74</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>8193565.74</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-2685346.552551758</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>2462064</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>2462064.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>31.67000000000001</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>32.27</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>32.27</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>2854768.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>3012758.2</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>3012758.2</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>5947125.2</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>8925246.32</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>8925246.32</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-2644177.302313902</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>2854768</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>2854768.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>32.29</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>32.29</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>1469139.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>3883096.4</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>3883096.4</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>8394042.6</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>9103186.62</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>9103186.619999999</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-2533004.612605754</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>1469139</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>1469139.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>32.4</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>32.32</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>4675377.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>5008192.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>5008192</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>20061078.4</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>9851668.88</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>9851668.880000001</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-2135261.784001052</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>4675377</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>4675377.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>32.86</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>32.31</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>32.31</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>3016605.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>5056833.8</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>5056833.8</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>22899336.4</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>9883789.8</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>9883789.800000001</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-1834323.893708583</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>3016605</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>3016605.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>33.12</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>32.44</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>32.28</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>3047902.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>6110902.0</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>6110902</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>25118237.3</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>9871501.58</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>9871501.58</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-1161175.482801178</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>3047902</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>3047902.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>33.22</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>32.22</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>32.22</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>7206459.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>8881492.2</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>8881492.199999999</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>27788001.9</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>9888488.0</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>9888488</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-161417.5928334147</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>7206459</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>7206459.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>33.97000000000001</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>7094617.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>12904988.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>12904988.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>27334017.0</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>9783605.2</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>9783605.199999999</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>827013.1997217275</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>7094617</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>7094617.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>34.73999999999999</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>32.09</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>32.09</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>4918586.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>35113964.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>35113964.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>26772613.7</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>9660599.88</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>9660599.880000001</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>2221504.074810442</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>4918586</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>4918586.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>32.84</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>32.91</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>32.91</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>2516966.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>3458477.4</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>3458477.4</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>5213929.6</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>5415877.02</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>5415877.02</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-383753.3493625773</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>2516966</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>2516966.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>32.78</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>32.84</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>32.9</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>3160810.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>3571106.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>3571106.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>5276222.9</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>5698977.36</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>5698977.36</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-252756.2706451491</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>3160810</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>3160810.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>32.77999999999999</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>32.87</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>32.9</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>3099064.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>5317981.2</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>5317981.2</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>5966548.1</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>5796005.24</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>5796005.24</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-125573.8628114965</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>3099064</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>3099064.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>32.77</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>32.89</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>32.89</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>32.89</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>5335365.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>6191631.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>6191631.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>5790386.6</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>5896767.16</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>5896767.16</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>67215.71490841918</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>5335365</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>5335365.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>32.92999999999999</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>32.94</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>32.91</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>32.91</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>3180182.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>7235396.6</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>7235396.6</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>5677661.1</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>6023320.34</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>6023320.34</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>100625.157547283</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>3180182</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>3180182.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>32.98999999999999</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>32.99</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>32.92</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>32.92</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>3080111.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>6969381.8</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>6969381.8</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>5682124.2</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>6140861.92</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>6140861.92</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>375671.6414046865</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>3080111</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>3080111.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>33.01000000000001</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>32.92</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>32.92</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>11895184.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>6981339.4</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>6981339.4</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>5695226.9</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>6327523.52</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>6327523.52</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>765900.2382936655</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>11895184</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>11895184.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>32.96</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>33.01</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>32.92</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>32.92</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>7467315.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>6615115.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>6615115</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>4860873.2</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>6247725.8</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>6247725.8</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>351543.9753388613</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>7467315</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>7467315.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>32.8</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>32.88</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>32.88</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>10554191.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>5389141.8</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>5389141.8</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>4755608.0</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>6186494.62</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>6186494.62</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>221465.8505698983</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>10554191</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>10554191.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>32.73</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>32.98</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>32.86</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>32.86</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>1850108.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>4119925.6</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>4119925.6</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>4224243.5</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>6094137.9</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>6094137.9</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-303006.2509061177</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>1850108</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>1850108.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>32.72</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>32.98</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>32.85</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>3139899.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>4394866.6</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>4394866.6</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>4508894.8</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>6144835.8</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>6144835.8</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-108850.1369109219</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>3139899</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>3139899.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>27.47</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>27.79</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>28.38</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>7904002.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>5622077.8</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>5622077.8</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>6793518.6</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>8580202.08</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>8580202.08</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-421935.4086029315</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>7904002</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>7904002.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>28.45</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>2230039.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>6023146.8</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>6023146.8</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>7140909.8</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>8636188.36</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>8636188.359999999</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-619864.545415963</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>2230039</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>2230039.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>27.23</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>28.54</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>28.54</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>5874915.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>7297820.8</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>7297820.8</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>7523259.6</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>8827085.08</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>8827085.08</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-272557.8285268657</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>5874915</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>5874915.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>27.55</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>27.84</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>28.63</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>28.63</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>6593026.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>8081896.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>8081896.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>8100217.9</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>8944822.02</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>8944822.02</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-157193.59623791</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>6593026</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>6593026.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>27.85</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>27.89</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>28.73</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>5508407.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>7512300.2</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>7512300.2</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>8191155.9</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>9045704.88</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>9045704.880000001</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-63713.95738804806</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>5508407</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>5508407.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>27.97</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>27.91</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>28.82</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>9909347.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>7964959.4</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>7964959.4</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>9023573.7</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>9364305.64</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>9364305.640000001</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>188313.0608756123</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>9909347</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>9909347.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>28.4</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>28.93</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>28.93</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>8603409.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>8258672.8</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>8258672.8</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>8547604.3</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>9526723.02</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>9526723.02</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>70096.90622100048</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>8603409</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>8603409.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>28.56</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>28.01</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>29.03</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>29.03</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>9795295.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>7748698.4</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>7748698.4</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>9020305.2</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>10106179.12</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>10106179.12</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>38635.15292080492</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>9795295</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>9795295.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>28.52</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>29.1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>3745043.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>8118539.0</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>8118539</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>8646202.1</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>15633612.04</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>15633612.04</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-135392.1072552186</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>3745043</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>3745043.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>28.37</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>29.18</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>7771703.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>8870011.6</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>8870011.6</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>8779158.0</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>17146768.28</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>17146768.28</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>269074.2391810063</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>7771703</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>7771703.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>28.23</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>29.25</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>11377914.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>10082188.0</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>10082188</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>8491430.7</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>17536215.56</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>17536215.56</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>405845.6541191489</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>11377914</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>11377914.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57633,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57817,11 @@
           <t>64.76</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>64.53</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>64.53</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57868,16 @@
           <t>585689.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>452104.2</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>452104.2</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>847136.2</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>770421.96</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>770421.96</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57894,10 @@
           <t>-38489.59520497138</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>585689</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>585689.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58063,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58247,11 @@
           <t>64.67999999999999</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>64.52</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>64.52</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58298,16 @@
           <t>129923.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>478339.6</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>478339.6</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>848505.9</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>770728.9</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>770728.9</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58324,10 @@
           <t>-38825.19412440713</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>129923</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>129923.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58493,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58677,11 @@
           <t>64.72</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>64.52</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>64.52</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58728,16 @@
           <t>407954.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>864705.0</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>864705</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>871010.3</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>772250.94</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>772250.9399999999</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58754,10 @@
           <t>10914.06435227068</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>407954</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>407954.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58923,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59107,11 @@
           <t>64.67999999999999</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>64.41</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>64.52</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>64.52</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59158,16 @@
           <t>748532.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>1082901.8</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>1082901.8</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>962509.6</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>769535.44</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>769535.4399999999</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59184,10 @@
           <t>51791.32416351489</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>748532</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>748532.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59353,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59537,11 @@
           <t>64.55999999999999</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>64.53</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>64.53</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59588,16 @@
           <t>388423.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>1203565.4</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>1203565.4</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>910731.7</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>773174.38</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>773174.38</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59614,10 @@
           <t>71847.21945945255</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>388423</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>388423.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59783,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59967,11 @@
           <t>64.47999999999999</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>64.38</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>64.53</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>64.53</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60018,16 @@
           <t>716866.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>1242168.2</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>1242168.2</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>888297.2</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>824956.04</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>824956.04</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60044,10 @@
           <t>136515.6334729544</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>716866</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>716866.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60213,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60397,11 @@
           <t>64.42</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>64.35</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>64.53</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>64.53</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60448,16 @@
           <t>2061750.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>1218672.2</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>1218672.2</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>870261.5</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>812576.32</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>812576.3199999999</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60474,10 @@
           <t>188833.2022967803</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>2061750</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>2061750.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60643,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60827,11 @@
           <t>64.36</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>64.34</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>64.53</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>64.53</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60878,16 @@
           <t>1498938.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>877315.6</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>877315.6</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>689241.6</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>776451.48</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>776451.48</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60904,10 @@
           <t>112733.8291059321</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>1498938</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>1498938.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61073,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61257,11 @@
           <t>64.34</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>64.32</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>64.52</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>64.52</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61308,16 @@
           <t>1351850.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>842117.4</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>842117.4</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>552981.0</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>756951.72</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>756951.72</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61334,10 @@
           <t>60295.51636522298</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>1351850</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>1351850.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61503,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61687,11 @@
           <t>64.42</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>64.33</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>64.53</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>64.53</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61738,16 @@
           <t>581437.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>617898.0</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>617898</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>477614.1</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>770871.96</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>770871.96</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61764,10 @@
           <t>-1010.341705976636</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>581437</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>581437.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61933,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62117,11 @@
           <t>64.28</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>64.34</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>64.57</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>64.56999999999999</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62168,16 @@
           <t>599386.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>534426.2</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>534426.2</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>475068.6</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>797347.58</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>797347.58</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62194,10 @@
           <t>-6009.805318191182</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>599386</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>599386.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
